--- a/artfynd/A 56420-2025 artfynd.xlsx
+++ b/artfynd/A 56420-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125539236</v>
+        <v>125539240</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599723</v>
+        <v>599745</v>
       </c>
       <c r="R2" t="n">
-        <v>7054699</v>
+        <v>7054750</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126046933</v>
+        <v>126045158</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599747</v>
+        <v>599602</v>
       </c>
       <c r="R3" t="n">
-        <v>7054579</v>
+        <v>7054659</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,50 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126048768</v>
+        <v>125539236</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599823</v>
+        <v>599723</v>
       </c>
       <c r="R4" t="n">
-        <v>7054600</v>
+        <v>7054699</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -939,17 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,50 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126047538</v>
+        <v>126046933</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599775</v>
+        <v>599747</v>
       </c>
       <c r="R5" t="n">
-        <v>7054583</v>
+        <v>7054579</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1052,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126045158</v>
+        <v>126048270</v>
       </c>
       <c r="B6" t="n">
-        <v>92535</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599602</v>
+        <v>599823</v>
       </c>
       <c r="R6" t="n">
-        <v>7054659</v>
+        <v>7054558</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1180,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126125219</v>
+        <v>126125233</v>
       </c>
       <c r="B7" t="n">
-        <v>79598</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599721</v>
+        <v>599795</v>
       </c>
       <c r="R7" t="n">
-        <v>7054693</v>
+        <v>7054649</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1277,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126125233</v>
+        <v>126125219</v>
       </c>
       <c r="B8" t="n">
-        <v>78738</v>
+        <v>79946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599795</v>
+        <v>599721</v>
       </c>
       <c r="R8" t="n">
-        <v>7054649</v>
+        <v>7054693</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1371,6 +1351,220 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126047538</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>599775</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7054583</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126048768</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>599823</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7054600</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56420-2025 artfynd.xlsx
+++ b/artfynd/A 56420-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125539240</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126045158</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125539236</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126046933</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126048270</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126125233</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126125219</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126047538</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,8 +1610,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126048768</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>